--- a/template/agent-template/agent/QA.xlsx
+++ b/template/agent-template/agent/QA.xlsx
@@ -429,7 +429,8 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Display as Suggested Question?</t>
+          <t>Display as Suggested Question?
+yes/no</t>
         </is>
       </c>
     </row>
